--- a/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -406,102 +406,102 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
-      <x:c r="A2" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="n">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="n">
+      <x:c r="A3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0" t="n">
+      <x:c r="A4" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="n">
+      <x:c r="B4" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="n">
+      <x:c r="C4" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="n">
+      <x:c r="D4" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="n">
+      <x:c r="E4" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="n">
+      <x:c r="F4" s="0">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
-      <x:c r="A5" s="0" t="n">
+      <x:c r="A5" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="n">
+      <x:c r="B5" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="n">
+      <x:c r="C5" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="n">
+      <x:c r="D5" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="n">
+      <x:c r="E5" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="n">
+      <x:c r="F5" s="0">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
-      <x:c r="A6" s="0" t="n">
+      <x:c r="A6" s="0">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="n">
+      <x:c r="B6" s="0">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="n">
+      <x:c r="C6" s="0">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="n">
+      <x:c r="D6" s="0">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="n">
+      <x:c r="E6" s="0">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="n">
+      <x:c r="F6" s="0">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -378,7 +378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -515,7 +515,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eec4d1a7-167c-48aa-90e5-5b9a36862be5}</x14:id>
+          <x14:id>{edfea128-b757-4abd-835b-1d9665ec78ae}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -529,7 +529,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e82188dc-c20b-47bb-aaa5-eb9eccff24d0}</x14:id>
+          <x14:id>{64a0c127-cd1e-4567-9d82-3849958112f9}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -543,7 +543,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc8d5093-2e00-4d66-96c4-a2936abd0ea8}</x14:id>
+          <x14:id>{ddc5755b-9d6a-4c43-be3f-ce954ea8aeaf}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -557,7 +557,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ed85cce-2633-44e0-a200-04513814e1ee}</x14:id>
+          <x14:id>{87f2776d-6448-4409-80e3-e2494b371e3c}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -571,7 +571,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed616d72-789c-4e30-9775-060eaa19c7c8}</x14:id>
+          <x14:id>{84400e88-282c-4d08-89f8-b2c41934654e}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -585,7 +585,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fdc881c-9f52-4e83-8072-8f4084a1426c}</x14:id>
+          <x14:id>{7e6d2e20-5873-450d-8036-681773a6e703}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -599,7 +599,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eec4d1a7-167c-48aa-90e5-5b9a36862be5}">
+          <x14:cfRule type="dataBar" id="{edfea128-b757-4abd-835b-1d9665ec78ae}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -610,7 +610,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e82188dc-c20b-47bb-aaa5-eb9eccff24d0}">
+          <x14:cfRule type="dataBar" id="{64a0c127-cd1e-4567-9d82-3849958112f9}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -625,7 +625,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc8d5093-2e00-4d66-96c4-a2936abd0ea8}">
+          <x14:cfRule type="dataBar" id="{ddc5755b-9d6a-4c43-be3f-ce954ea8aeaf}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -640,7 +640,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5ed85cce-2633-44e0-a200-04513814e1ee}">
+          <x14:cfRule type="dataBar" id="{87f2776d-6448-4409-80e3-e2494b371e3c}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -655,7 +655,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ed616d72-789c-4e30-9775-060eaa19c7c8}">
+          <x14:cfRule type="dataBar" id="{84400e88-282c-4d08-89f8-b2c41934654e}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -670,7 +670,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9fdc881c-9f52-4e83-8072-8f4084a1426c}">
+          <x14:cfRule type="dataBar" id="{7e6d2e20-5873-450d-8036-681773a6e703}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>

--- a/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Automatic</x:t>
   </x:si>
@@ -378,7 +378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -515,7 +515,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{edfea128-b757-4abd-835b-1d9665ec78ae}</x14:id>
+          <x14:id>{0919a367-36c7-49f9-b2ba-d6dc56327ace}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -529,7 +529,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64a0c127-cd1e-4567-9d82-3849958112f9}</x14:id>
+          <x14:id>{87956b1a-8603-4cb5-8097-e394c4a1a11f}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -543,7 +543,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ddc5755b-9d6a-4c43-be3f-ce954ea8aeaf}</x14:id>
+          <x14:id>{8b695999-07ce-44f4-acd8-0ec973c91ac4}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -557,7 +557,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87f2776d-6448-4409-80e3-e2494b371e3c}</x14:id>
+          <x14:id>{20b1bd6d-72e9-475a-a31b-47d4e6254047}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -571,7 +571,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84400e88-282c-4d08-89f8-b2c41934654e}</x14:id>
+          <x14:id>{4c905630-3417-4a98-84f8-3d5d4790ba69}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -585,7 +585,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e6d2e20-5873-450d-8036-681773a6e703}</x14:id>
+          <x14:id>{d9e119f7-9070-4057-905e-0bfd82b7fbe8}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -599,7 +599,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{edfea128-b757-4abd-835b-1d9665ec78ae}">
+          <x14:cfRule type="dataBar" id="{0919a367-36c7-49f9-b2ba-d6dc56327ace}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -610,7 +610,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{64a0c127-cd1e-4567-9d82-3849958112f9}">
+          <x14:cfRule type="dataBar" id="{87956b1a-8603-4cb5-8097-e394c4a1a11f}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -625,7 +625,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ddc5755b-9d6a-4c43-be3f-ce954ea8aeaf}">
+          <x14:cfRule type="dataBar" id="{8b695999-07ce-44f4-acd8-0ec973c91ac4}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -640,7 +640,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{87f2776d-6448-4409-80e3-e2494b371e3c}">
+          <x14:cfRule type="dataBar" id="{20b1bd6d-72e9-475a-a31b-47d4e6254047}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -655,7 +655,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84400e88-282c-4d08-89f8-b2c41934654e}">
+          <x14:cfRule type="dataBar" id="{4c905630-3417-4a98-84f8-3d5d4790ba69}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -670,7 +670,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e6d2e20-5873-450d-8036-681773a6e703}">
+          <x14:cfRule type="dataBar" id="{d9e119f7-9070-4057-905e-0bfd82b7fbe8}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>

--- a/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -6,7 +6,7 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -515,7 +515,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0919a367-36c7-49f9-b2ba-d6dc56327ace}</x14:id>
+          <x14:id>{38d9e5d3-73a7-4e18-b3b9-aa1b26e4cc06}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -529,7 +529,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87956b1a-8603-4cb5-8097-e394c4a1a11f}</x14:id>
+          <x14:id>{0671ebad-2a52-43f6-a3a9-585018af6f01}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -543,7 +543,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b695999-07ce-44f4-acd8-0ec973c91ac4}</x14:id>
+          <x14:id>{0b10551c-b4e0-4975-ac10-c045e09df4bf}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -557,7 +557,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20b1bd6d-72e9-475a-a31b-47d4e6254047}</x14:id>
+          <x14:id>{49ad88bb-d5a9-4684-afcc-8033d8d051eb}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -571,7 +571,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c905630-3417-4a98-84f8-3d5d4790ba69}</x14:id>
+          <x14:id>{93055e58-8649-4a74-9a8e-1e4036062ece}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -585,7 +585,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d9e119f7-9070-4057-905e-0bfd82b7fbe8}</x14:id>
+          <x14:id>{01b3b3bb-243e-4add-ae5b-fd208d5e5960}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -599,7 +599,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0919a367-36c7-49f9-b2ba-d6dc56327ace}">
+          <x14:cfRule type="dataBar" id="{38d9e5d3-73a7-4e18-b3b9-aa1b26e4cc06}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -610,7 +610,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{87956b1a-8603-4cb5-8097-e394c4a1a11f}">
+          <x14:cfRule type="dataBar" id="{0671ebad-2a52-43f6-a3a9-585018af6f01}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -625,7 +625,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8b695999-07ce-44f4-acd8-0ec973c91ac4}">
+          <x14:cfRule type="dataBar" id="{0b10551c-b4e0-4975-ac10-c045e09df4bf}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -640,7 +640,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20b1bd6d-72e9-475a-a31b-47d4e6254047}">
+          <x14:cfRule type="dataBar" id="{49ad88bb-d5a9-4684-afcc-8033d8d051eb}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -655,7 +655,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c905630-3417-4a98-84f8-3d5d4790ba69}">
+          <x14:cfRule type="dataBar" id="{93055e58-8649-4a74-9a8e-1e4036062ece}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -670,7 +670,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d9e119f7-9070-4057-905e-0bfd82b7fbe8}">
+          <x14:cfRule type="dataBar" id="{01b3b3bb-243e-4add-ae5b-fd208d5e5960}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>
